--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194502</v>
+        <v>131194525</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582445</v>
+        <v>582468</v>
       </c>
       <c r="R3" t="n">
-        <v>6971210</v>
+        <v>6971420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B4" t="n">
-        <v>91808</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R4" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194525</v>
+        <v>131194502</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1033,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582468</v>
+        <v>582445</v>
       </c>
       <c r="R5" t="n">
-        <v>6971420</v>
+        <v>6971210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,12 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R6" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>80348</v>
+        <v>91808</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R7" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>91808</v>
+        <v>80348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R8" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194515</v>
+        <v>131194505</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>91808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582399</v>
+        <v>582448</v>
       </c>
       <c r="R12" t="n">
-        <v>6971300</v>
+        <v>6971239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194505</v>
+        <v>131194515</v>
       </c>
       <c r="B13" t="n">
-        <v>91808</v>
+        <v>92106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582448</v>
+        <v>582399</v>
       </c>
       <c r="R13" t="n">
-        <v>6971239</v>
+        <v>6971300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B17" t="n">
-        <v>91808</v>
+        <v>80348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R17" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B18" t="n">
-        <v>80348</v>
+        <v>91808</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R18" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B25" t="n">
-        <v>79243</v>
+        <v>80308</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R25" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B26" t="n">
-        <v>80308</v>
+        <v>79243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R26" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B27" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,34 +3426,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R27" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,42 +3546,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R28" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3605,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,12 +3615,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3642,7 +3642,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131194526</v>
+        <v>131194517</v>
       </c>
       <c r="B29" t="n">
         <v>80348</v>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582489</v>
+        <v>582448</v>
       </c>
       <c r="R29" t="n">
-        <v>6971407</v>
+        <v>6971341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3749,32 +3749,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131194519</v>
+        <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>5197</v>
+        <v>80348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582458</v>
+        <v>582489</v>
       </c>
       <c r="R30" t="n">
-        <v>6971363</v>
+        <v>6971407</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,45 +3856,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131194517</v>
+        <v>131194519</v>
       </c>
       <c r="B31" t="n">
-        <v>80348</v>
+        <v>5197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582448</v>
+        <v>582458</v>
       </c>
       <c r="R31" t="n">
-        <v>6971341</v>
+        <v>6971363</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3926,7 +3935,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3936,7 +3945,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3945,6 +3954,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194522</v>
       </c>
       <c r="B2" t="n">
-        <v>80308</v>
+        <v>80309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194525</v>
+        <v>131194520</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582468</v>
+        <v>582466</v>
       </c>
       <c r="R3" t="n">
-        <v>6971420</v>
+        <v>6971369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194497</v>
+        <v>131194502</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>92107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582449</v>
+        <v>582445</v>
       </c>
       <c r="R4" t="n">
-        <v>6971290</v>
+        <v>6971210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194502</v>
+        <v>131194525</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582445</v>
+        <v>582468</v>
       </c>
       <c r="R5" t="n">
-        <v>6971210</v>
+        <v>6971420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1084,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B6" t="n">
-        <v>91808</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,34 +1127,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R6" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1239,7 @@
         <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>91808</v>
+        <v>91809</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>131194523</v>
       </c>
       <c r="B9" t="n">
-        <v>80383</v>
+        <v>80384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>131194501</v>
       </c>
       <c r="B10" t="n">
-        <v>80252</v>
+        <v>80253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194506</v>
+        <v>131194505</v>
       </c>
       <c r="B11" t="n">
-        <v>80377</v>
+        <v>91809</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582440</v>
+        <v>582448</v>
       </c>
       <c r="R11" t="n">
-        <v>6971241</v>
+        <v>6971239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,32 +1771,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194505</v>
+        <v>131194506</v>
       </c>
       <c r="B12" t="n">
-        <v>91808</v>
+        <v>80378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582448</v>
+        <v>582440</v>
       </c>
       <c r="R12" t="n">
-        <v>6971239</v>
+        <v>6971241</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,7 +1881,7 @@
         <v>131194515</v>
       </c>
       <c r="B13" t="n">
-        <v>92106</v>
+        <v>92107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194499</v>
+        <v>131194508</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,42 +1996,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582482</v>
+        <v>582438</v>
       </c>
       <c r="R14" t="n">
-        <v>6971060</v>
+        <v>6971241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194508</v>
+        <v>131194498</v>
       </c>
       <c r="B15" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582438</v>
+        <v>582466</v>
       </c>
       <c r="R15" t="n">
-        <v>6971241</v>
+        <v>6971193</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194498</v>
+        <v>131194499</v>
       </c>
       <c r="B16" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,34 +2210,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582466</v>
+        <v>582482</v>
       </c>
       <c r="R16" t="n">
-        <v>6971193</v>
+        <v>6971060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>80348</v>
+        <v>91809</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R17" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>91808</v>
+        <v>80349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R18" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2776,7 +2776,7 @@
         <v>131194510</v>
       </c>
       <c r="B21" t="n">
-        <v>80308</v>
+        <v>80309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>131194507</v>
       </c>
       <c r="B22" t="n">
-        <v>80308</v>
+        <v>80309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131194524</v>
       </c>
       <c r="B24" t="n">
-        <v>80384</v>
+        <v>80385</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>80308</v>
+        <v>79244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R25" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>80309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R26" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,7 +3538,7 @@
         <v>131194521</v>
       </c>
       <c r="B28" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>131194517</v>
       </c>
       <c r="B29" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -1664,32 +1664,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194505</v>
+        <v>131194506</v>
       </c>
       <c r="B11" t="n">
-        <v>91809</v>
+        <v>80378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582448</v>
+        <v>582440</v>
       </c>
       <c r="R11" t="n">
-        <v>6971239</v>
+        <v>6971241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,32 +1771,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194506</v>
+        <v>131194515</v>
       </c>
       <c r="B12" t="n">
-        <v>80378</v>
+        <v>92107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582440</v>
+        <v>582399</v>
       </c>
       <c r="R12" t="n">
-        <v>6971241</v>
+        <v>6971300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194515</v>
+        <v>131194505</v>
       </c>
       <c r="B13" t="n">
-        <v>92107</v>
+        <v>91809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582399</v>
+        <v>582448</v>
       </c>
       <c r="R13" t="n">
-        <v>6971300</v>
+        <v>6971239</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,42 +3426,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R27" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3485,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3495,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B28" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,34 +3533,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R28" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3615,7 +3610,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -1664,32 +1664,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194506</v>
+        <v>131194515</v>
       </c>
       <c r="B11" t="n">
-        <v>80378</v>
+        <v>92107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582440</v>
+        <v>582399</v>
       </c>
       <c r="R11" t="n">
-        <v>6971241</v>
+        <v>6971300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194515</v>
+        <v>131194505</v>
       </c>
       <c r="B12" t="n">
-        <v>92107</v>
+        <v>91809</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582399</v>
+        <v>582448</v>
       </c>
       <c r="R12" t="n">
-        <v>6971300</v>
+        <v>6971239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194505</v>
+        <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>91809</v>
+        <v>80378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582448</v>
+        <v>582440</v>
       </c>
       <c r="R13" t="n">
-        <v>6971239</v>
+        <v>6971241</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194508</v>
+        <v>131194499</v>
       </c>
       <c r="B14" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,34 +1996,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582438</v>
+        <v>582482</v>
       </c>
       <c r="R14" t="n">
-        <v>6971241</v>
+        <v>6971060</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194498</v>
+        <v>131194508</v>
       </c>
       <c r="B15" t="n">
         <v>80349</v>
@@ -2127,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582466</v>
+        <v>582438</v>
       </c>
       <c r="R15" t="n">
-        <v>6971193</v>
+        <v>6971241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194499</v>
+        <v>131194498</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,42 +2223,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582482</v>
+        <v>582466</v>
       </c>
       <c r="R16" t="n">
-        <v>6971060</v>
+        <v>6971193</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,12 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B17" t="n">
-        <v>91809</v>
+        <v>80349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R17" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B18" t="n">
-        <v>80349</v>
+        <v>91809</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R18" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>80309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R25" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B26" t="n">
-        <v>80309</v>
+        <v>79244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R26" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B27" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,34 +3426,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R27" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,42 +3546,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R28" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3605,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,12 +3615,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194520</v>
+        <v>131194502</v>
       </c>
       <c r="B3" t="n">
-        <v>91809</v>
+        <v>92107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582466</v>
+        <v>582445</v>
       </c>
       <c r="R3" t="n">
-        <v>6971369</v>
+        <v>6971210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194502</v>
+        <v>131194520</v>
       </c>
       <c r="B4" t="n">
-        <v>92107</v>
+        <v>91809</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582445</v>
+        <v>582466</v>
       </c>
       <c r="R4" t="n">
-        <v>6971210</v>
+        <v>6971369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1664,32 +1664,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194515</v>
+        <v>131194506</v>
       </c>
       <c r="B11" t="n">
-        <v>92107</v>
+        <v>80378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582399</v>
+        <v>582440</v>
       </c>
       <c r="R11" t="n">
-        <v>6971300</v>
+        <v>6971241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194506</v>
+        <v>131194515</v>
       </c>
       <c r="B13" t="n">
-        <v>80378</v>
+        <v>92107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582440</v>
+        <v>582399</v>
       </c>
       <c r="R13" t="n">
-        <v>6971241</v>
+        <v>6971300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194499</v>
+        <v>131194508</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,42 +1996,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582482</v>
+        <v>582438</v>
       </c>
       <c r="R14" t="n">
-        <v>6971060</v>
+        <v>6971241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,7 +2092,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194508</v>
+        <v>131194498</v>
       </c>
       <c r="B15" t="n">
         <v>80349</v>
@@ -2140,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582438</v>
+        <v>582466</v>
       </c>
       <c r="R15" t="n">
-        <v>6971241</v>
+        <v>6971193</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194498</v>
+        <v>131194499</v>
       </c>
       <c r="B16" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,34 +2210,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582466</v>
+        <v>582482</v>
       </c>
       <c r="R16" t="n">
-        <v>6971193</v>
+        <v>6971060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>80349</v>
+        <v>91809</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R17" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>91809</v>
+        <v>80349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R18" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>80309</v>
+        <v>79244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R25" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>79244</v>
+        <v>80309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R26" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,42 +3426,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R27" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3485,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3495,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B28" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,34 +3533,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R28" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3615,7 +3610,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194502</v>
+        <v>131194520</v>
       </c>
       <c r="B3" t="n">
-        <v>92107</v>
+        <v>91809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582445</v>
+        <v>582466</v>
       </c>
       <c r="R3" t="n">
-        <v>6971210</v>
+        <v>6971369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194520</v>
+        <v>131194502</v>
       </c>
       <c r="B4" t="n">
-        <v>91809</v>
+        <v>92107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582466</v>
+        <v>582445</v>
       </c>
       <c r="R4" t="n">
-        <v>6971369</v>
+        <v>6971210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194525</v>
+        <v>131194497</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1029,7 +1029,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582468</v>
+        <v>582449</v>
       </c>
       <c r="R5" t="n">
-        <v>6971420</v>
+        <v>6971290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194497</v>
+        <v>131194525</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1149,7 +1149,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582449</v>
+        <v>582468</v>
       </c>
       <c r="R6" t="n">
-        <v>6971290</v>
+        <v>6971420</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1664,32 +1664,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194506</v>
+        <v>131194515</v>
       </c>
       <c r="B11" t="n">
-        <v>80378</v>
+        <v>92107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582440</v>
+        <v>582399</v>
       </c>
       <c r="R11" t="n">
-        <v>6971241</v>
+        <v>6971300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194515</v>
+        <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>92107</v>
+        <v>80378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582399</v>
+        <v>582440</v>
       </c>
       <c r="R13" t="n">
-        <v>6971300</v>
+        <v>6971241</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B27" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,34 +3426,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R27" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,42 +3546,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R28" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3605,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,12 +3615,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194522</v>
       </c>
       <c r="B2" t="n">
-        <v>80309</v>
+        <v>80310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194520</v>
+        <v>131194525</v>
       </c>
       <c r="B3" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582466</v>
+        <v>582468</v>
       </c>
       <c r="R3" t="n">
-        <v>6971369</v>
+        <v>6971420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194502</v>
+        <v>131194520</v>
       </c>
       <c r="B4" t="n">
-        <v>92107</v>
+        <v>91810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582445</v>
+        <v>582466</v>
       </c>
       <c r="R4" t="n">
-        <v>6971210</v>
+        <v>6971369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194497</v>
+        <v>131194502</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582449</v>
+        <v>582445</v>
       </c>
       <c r="R5" t="n">
-        <v>6971290</v>
+        <v>6971210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,12 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194525</v>
+        <v>131194497</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1149,7 +1149,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582468</v>
+        <v>582449</v>
       </c>
       <c r="R6" t="n">
-        <v>6971420</v>
+        <v>6971290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B7" t="n">
-        <v>91809</v>
+        <v>80350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R7" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B8" t="n">
-        <v>80349</v>
+        <v>91810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R8" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194523</v>
+        <v>131194501</v>
       </c>
       <c r="B9" t="n">
-        <v>80384</v>
+        <v>80254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582470</v>
+        <v>582435</v>
       </c>
       <c r="R9" t="n">
-        <v>6971407</v>
+        <v>6971209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194501</v>
+        <v>131194523</v>
       </c>
       <c r="B10" t="n">
-        <v>80253</v>
+        <v>80385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582435</v>
+        <v>582470</v>
       </c>
       <c r="R10" t="n">
-        <v>6971209</v>
+        <v>6971407</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,7 +1667,7 @@
         <v>131194515</v>
       </c>
       <c r="B11" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>131194505</v>
       </c>
       <c r="B12" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>80378</v>
+        <v>80379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>131194508</v>
       </c>
       <c r="B14" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>131194498</v>
       </c>
       <c r="B15" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>131194510</v>
       </c>
       <c r="B21" t="n">
-        <v>80309</v>
+        <v>80310</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>131194507</v>
       </c>
       <c r="B22" t="n">
-        <v>80309</v>
+        <v>80310</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131194524</v>
       </c>
       <c r="B24" t="n">
-        <v>80385</v>
+        <v>80386</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>80309</v>
+        <v>80310</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,42 +3426,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R27" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3485,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3495,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B28" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,34 +3533,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R28" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3615,7 +3610,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,7 +3645,7 @@
         <v>131194517</v>
       </c>
       <c r="B29" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>80310</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R25" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B26" t="n">
-        <v>80310</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R26" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194525</v>
+        <v>131194520</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>91810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582468</v>
+        <v>582466</v>
       </c>
       <c r="R3" t="n">
-        <v>6971420</v>
+        <v>6971369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194520</v>
+        <v>131194502</v>
       </c>
       <c r="B4" t="n">
-        <v>91810</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582466</v>
+        <v>582445</v>
       </c>
       <c r="R4" t="n">
-        <v>6971369</v>
+        <v>6971210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194502</v>
+        <v>131194525</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582445</v>
+        <v>582468</v>
       </c>
       <c r="R5" t="n">
-        <v>6971210</v>
+        <v>6971420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1084,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>80310</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R25" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>80310</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R26" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194520</v>
+        <v>131194525</v>
       </c>
       <c r="B3" t="n">
-        <v>91810</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582466</v>
+        <v>582468</v>
       </c>
       <c r="R3" t="n">
-        <v>6971369</v>
+        <v>6971420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194502</v>
+        <v>131194497</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582445</v>
+        <v>582449</v>
       </c>
       <c r="R4" t="n">
-        <v>6971210</v>
+        <v>6971290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194525</v>
+        <v>131194502</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1033,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582468</v>
+        <v>582445</v>
       </c>
       <c r="R5" t="n">
-        <v>6971420</v>
+        <v>6971210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,12 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R6" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>80350</v>
+        <v>91813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R7" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>91810</v>
+        <v>80350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R8" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194501</v>
+        <v>131194523</v>
       </c>
       <c r="B9" t="n">
-        <v>80254</v>
+        <v>80385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582435</v>
+        <v>582470</v>
       </c>
       <c r="R9" t="n">
-        <v>6971209</v>
+        <v>6971407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194523</v>
+        <v>131194501</v>
       </c>
       <c r="B10" t="n">
-        <v>80385</v>
+        <v>80254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582470</v>
+        <v>582435</v>
       </c>
       <c r="R10" t="n">
-        <v>6971407</v>
+        <v>6971209</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,32 +1664,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194515</v>
+        <v>131194506</v>
       </c>
       <c r="B11" t="n">
-        <v>92108</v>
+        <v>80379</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582399</v>
+        <v>582440</v>
       </c>
       <c r="R11" t="n">
-        <v>6971300</v>
+        <v>6971241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,7 +1774,7 @@
         <v>131194505</v>
       </c>
       <c r="B12" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194506</v>
+        <v>131194515</v>
       </c>
       <c r="B13" t="n">
-        <v>80379</v>
+        <v>92111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582440</v>
+        <v>582399</v>
       </c>
       <c r="R13" t="n">
-        <v>6971241</v>
+        <v>6971300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2322,7 +2322,7 @@
         <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91773</v>
+        <v>91776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194522</v>
       </c>
       <c r="B2" t="n">
-        <v>80310</v>
+        <v>80311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194525</v>
+        <v>131194502</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>92112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582468</v>
+        <v>582445</v>
       </c>
       <c r="R3" t="n">
-        <v>6971420</v>
+        <v>6971210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91814</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R4" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194502</v>
+        <v>131194525</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582445</v>
+        <v>582468</v>
       </c>
       <c r="R5" t="n">
-        <v>6971210</v>
+        <v>6971420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1084,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B6" t="n">
-        <v>91813</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,34 +1127,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R6" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B7" t="n">
-        <v>91813</v>
+        <v>80351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R7" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B8" t="n">
-        <v>80350</v>
+        <v>91814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R8" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194523</v>
+        <v>131194501</v>
       </c>
       <c r="B9" t="n">
-        <v>80385</v>
+        <v>80255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582470</v>
+        <v>582435</v>
       </c>
       <c r="R9" t="n">
-        <v>6971407</v>
+        <v>6971209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194501</v>
+        <v>131194523</v>
       </c>
       <c r="B10" t="n">
-        <v>80254</v>
+        <v>80386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582435</v>
+        <v>582470</v>
       </c>
       <c r="R10" t="n">
-        <v>6971209</v>
+        <v>6971407</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,32 +1664,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194506</v>
+        <v>131194515</v>
       </c>
       <c r="B11" t="n">
-        <v>80379</v>
+        <v>92112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582440</v>
+        <v>582399</v>
       </c>
       <c r="R11" t="n">
-        <v>6971241</v>
+        <v>6971300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,7 +1774,7 @@
         <v>131194505</v>
       </c>
       <c r="B12" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194515</v>
+        <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>92111</v>
+        <v>80380</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582399</v>
+        <v>582440</v>
       </c>
       <c r="R13" t="n">
-        <v>6971300</v>
+        <v>6971241</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,7 +1988,7 @@
         <v>131194508</v>
       </c>
       <c r="B14" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>131194498</v>
       </c>
       <c r="B15" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>131194510</v>
       </c>
       <c r="B21" t="n">
-        <v>80310</v>
+        <v>80311</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>131194507</v>
       </c>
       <c r="B22" t="n">
-        <v>80310</v>
+        <v>80311</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131194524</v>
       </c>
       <c r="B24" t="n">
-        <v>80386</v>
+        <v>80387</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>80310</v>
+        <v>80311</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>131194521</v>
       </c>
       <c r="B27" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>131194517</v>
       </c>
       <c r="B29" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194501</v>
+        <v>131194523</v>
       </c>
       <c r="B9" t="n">
-        <v>80255</v>
+        <v>80386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582435</v>
+        <v>582470</v>
       </c>
       <c r="R9" t="n">
-        <v>6971209</v>
+        <v>6971407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194523</v>
+        <v>131194501</v>
       </c>
       <c r="B10" t="n">
-        <v>80386</v>
+        <v>80255</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582470</v>
+        <v>582435</v>
       </c>
       <c r="R10" t="n">
-        <v>6971407</v>
+        <v>6971209</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1985,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194508</v>
+        <v>131194499</v>
       </c>
       <c r="B14" t="n">
-        <v>80351</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,34 +1996,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582438</v>
+        <v>582482</v>
       </c>
       <c r="R14" t="n">
-        <v>6971241</v>
+        <v>6971060</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194498</v>
+        <v>131194508</v>
       </c>
       <c r="B15" t="n">
         <v>80351</v>
@@ -2127,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582466</v>
+        <v>582438</v>
       </c>
       <c r="R15" t="n">
-        <v>6971193</v>
+        <v>6971241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194499</v>
+        <v>131194498</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,42 +2223,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582482</v>
+        <v>582466</v>
       </c>
       <c r="R16" t="n">
-        <v>6971060</v>
+        <v>6971193</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,12 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194522</v>
       </c>
       <c r="B2" t="n">
-        <v>80311</v>
+        <v>80313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194502</v>
+        <v>131194525</v>
       </c>
       <c r="B3" t="n">
-        <v>92112</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582445</v>
+        <v>582468</v>
       </c>
       <c r="R3" t="n">
-        <v>6971210</v>
+        <v>6971420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B4" t="n">
-        <v>91814</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R4" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194525</v>
+        <v>131194502</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>92114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1033,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582468</v>
+        <v>582445</v>
       </c>
       <c r="R5" t="n">
-        <v>6971420</v>
+        <v>6971210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,12 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R6" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>80351</v>
+        <v>91816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R7" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>91814</v>
+        <v>80353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R8" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194523</v>
+        <v>131194501</v>
       </c>
       <c r="B9" t="n">
-        <v>80386</v>
+        <v>80257</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582470</v>
+        <v>582435</v>
       </c>
       <c r="R9" t="n">
-        <v>6971407</v>
+        <v>6971209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194501</v>
+        <v>131194523</v>
       </c>
       <c r="B10" t="n">
-        <v>80255</v>
+        <v>80388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582435</v>
+        <v>582470</v>
       </c>
       <c r="R10" t="n">
-        <v>6971209</v>
+        <v>6971407</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194515</v>
+        <v>131194505</v>
       </c>
       <c r="B11" t="n">
-        <v>92112</v>
+        <v>91816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582399</v>
+        <v>582448</v>
       </c>
       <c r="R11" t="n">
-        <v>6971300</v>
+        <v>6971239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194505</v>
+        <v>131194515</v>
       </c>
       <c r="B12" t="n">
-        <v>91814</v>
+        <v>92114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582448</v>
+        <v>582399</v>
       </c>
       <c r="R12" t="n">
-        <v>6971239</v>
+        <v>6971300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,7 +1881,7 @@
         <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>131194499</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>131194508</v>
       </c>
       <c r="B15" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>131194498</v>
       </c>
       <c r="B16" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>131194513</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>131194504</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>131194510</v>
       </c>
       <c r="B21" t="n">
-        <v>80311</v>
+        <v>80313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>131194507</v>
       </c>
       <c r="B22" t="n">
-        <v>80311</v>
+        <v>80313</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131194524</v>
       </c>
       <c r="B24" t="n">
-        <v>80387</v>
+        <v>80389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>80313</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R25" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B26" t="n">
-        <v>80311</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R26" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B27" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,34 +3426,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R27" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>80353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,42 +3546,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R28" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3605,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,12 +3615,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,7 +3645,7 @@
         <v>131194517</v>
       </c>
       <c r="B29" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194522</v>
       </c>
       <c r="B2" t="n">
-        <v>80313</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194525</v>
+        <v>131194502</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582468</v>
+        <v>582445</v>
       </c>
       <c r="R3" t="n">
-        <v>6971420</v>
+        <v>6971210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>91817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R4" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194502</v>
+        <v>131194525</v>
       </c>
       <c r="B5" t="n">
-        <v>92114</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582445</v>
+        <v>582468</v>
       </c>
       <c r="R5" t="n">
-        <v>6971210</v>
+        <v>6971420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1084,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B6" t="n">
-        <v>91816</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,34 +1127,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R6" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1239,7 @@
         <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194501</v>
+        <v>131194523</v>
       </c>
       <c r="B9" t="n">
-        <v>80257</v>
+        <v>80389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582435</v>
+        <v>582470</v>
       </c>
       <c r="R9" t="n">
-        <v>6971209</v>
+        <v>6971407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194523</v>
+        <v>131194501</v>
       </c>
       <c r="B10" t="n">
-        <v>80388</v>
+        <v>80258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582470</v>
+        <v>582435</v>
       </c>
       <c r="R10" t="n">
-        <v>6971407</v>
+        <v>6971209</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,7 +1667,7 @@
         <v>131194505</v>
       </c>
       <c r="B11" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>131194515</v>
       </c>
       <c r="B12" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>80382</v>
+        <v>80383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194499</v>
+        <v>131194508</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,42 +1996,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582482</v>
+        <v>582438</v>
       </c>
       <c r="R14" t="n">
-        <v>6971060</v>
+        <v>6971241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194508</v>
+        <v>131194498</v>
       </c>
       <c r="B15" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582438</v>
+        <v>582466</v>
       </c>
       <c r="R15" t="n">
-        <v>6971241</v>
+        <v>6971193</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194498</v>
+        <v>131194499</v>
       </c>
       <c r="B16" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,34 +2210,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582466</v>
+        <v>582482</v>
       </c>
       <c r="R16" t="n">
-        <v>6971193</v>
+        <v>6971060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,7 +2322,7 @@
         <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>131194513</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>131194504</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>131194510</v>
       </c>
       <c r="B21" t="n">
-        <v>80313</v>
+        <v>80314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>131194507</v>
       </c>
       <c r="B22" t="n">
-        <v>80313</v>
+        <v>80314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131194524</v>
       </c>
       <c r="B24" t="n">
-        <v>80389</v>
+        <v>80390</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>80313</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R25" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>80314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R26" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,42 +3426,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R27" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3485,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3495,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B28" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,34 +3533,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R28" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3615,7 +3610,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,7 +3645,7 @@
         <v>131194517</v>
       </c>
       <c r="B29" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194520</v>
+        <v>131194525</v>
       </c>
       <c r="B4" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582466</v>
+        <v>582468</v>
       </c>
       <c r="R4" t="n">
-        <v>6971369</v>
+        <v>6971420</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194525</v>
+        <v>131194497</v>
       </c>
       <c r="B5" t="n">
         <v>57887</v>
@@ -1029,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1039,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582468</v>
+        <v>582449</v>
       </c>
       <c r="R5" t="n">
-        <v>6971420</v>
+        <v>6971290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,12 +1097,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>91817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R6" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B7" t="n">
-        <v>91817</v>
+        <v>80354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R7" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B8" t="n">
-        <v>80354</v>
+        <v>91817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R8" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194505</v>
+        <v>131194515</v>
       </c>
       <c r="B11" t="n">
-        <v>91817</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582448</v>
+        <v>582399</v>
       </c>
       <c r="R11" t="n">
-        <v>6971239</v>
+        <v>6971300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,32 +1771,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194515</v>
+        <v>131194506</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>80383</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582399</v>
+        <v>582440</v>
       </c>
       <c r="R12" t="n">
-        <v>6971300</v>
+        <v>6971241</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194506</v>
+        <v>131194505</v>
       </c>
       <c r="B13" t="n">
-        <v>80383</v>
+        <v>91817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582440</v>
+        <v>582448</v>
       </c>
       <c r="R13" t="n">
-        <v>6971241</v>
+        <v>6971239</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B17" t="n">
-        <v>91817</v>
+        <v>80354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R17" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B18" t="n">
-        <v>80354</v>
+        <v>91817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R18" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194525</v>
+        <v>131194520</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>91817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582468</v>
+        <v>582466</v>
       </c>
       <c r="R4" t="n">
-        <v>6971420</v>
+        <v>6971369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194497</v>
+        <v>131194525</v>
       </c>
       <c r="B5" t="n">
         <v>57887</v>
@@ -1042,7 +1029,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582449</v>
+        <v>582468</v>
       </c>
       <c r="R5" t="n">
-        <v>6971290</v>
+        <v>6971420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,12 +1084,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B6" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,34 +1127,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R6" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>80354</v>
+        <v>91817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R7" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>91817</v>
+        <v>80354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R8" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194515</v>
+        <v>131194505</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
+        <v>91817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582399</v>
+        <v>582448</v>
       </c>
       <c r="R11" t="n">
-        <v>6971300</v>
+        <v>6971239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,32 +1771,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194506</v>
+        <v>131194515</v>
       </c>
       <c r="B12" t="n">
-        <v>80383</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582440</v>
+        <v>582399</v>
       </c>
       <c r="R12" t="n">
-        <v>6971241</v>
+        <v>6971300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194505</v>
+        <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>91817</v>
+        <v>80383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582448</v>
+        <v>582440</v>
       </c>
       <c r="R13" t="n">
-        <v>6971239</v>
+        <v>6971241</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>80354</v>
+        <v>91817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R17" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>91817</v>
+        <v>80354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R18" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194522</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>80315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131194502</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B4" t="n">
-        <v>91817</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R4" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +1012,7 @@
         <v>131194525</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>91818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R6" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1239,7 @@
         <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>131194523</v>
       </c>
       <c r="B9" t="n">
-        <v>80389</v>
+        <v>80390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>131194501</v>
       </c>
       <c r="B10" t="n">
-        <v>80258</v>
+        <v>80259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>131194505</v>
       </c>
       <c r="B11" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>131194515</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>80383</v>
+        <v>80384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194508</v>
+        <v>131194499</v>
       </c>
       <c r="B14" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,34 +1996,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582438</v>
+        <v>582482</v>
       </c>
       <c r="R14" t="n">
-        <v>6971241</v>
+        <v>6971060</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194498</v>
+        <v>131194508</v>
       </c>
       <c r="B15" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582466</v>
+        <v>582438</v>
       </c>
       <c r="R15" t="n">
-        <v>6971193</v>
+        <v>6971241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194499</v>
+        <v>131194498</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,42 +2223,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582482</v>
+        <v>582466</v>
       </c>
       <c r="R16" t="n">
-        <v>6971060</v>
+        <v>6971193</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,12 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,7 +2322,7 @@
         <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>131194513</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>131194504</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194510</v>
+        <v>131194507</v>
       </c>
       <c r="B21" t="n">
-        <v>80314</v>
+        <v>80315</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582423</v>
+        <v>582437</v>
       </c>
       <c r="R21" t="n">
-        <v>6971254</v>
+        <v>6971241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194507</v>
+        <v>131194510</v>
       </c>
       <c r="B22" t="n">
-        <v>80314</v>
+        <v>80315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582437</v>
+        <v>582423</v>
       </c>
       <c r="R22" t="n">
-        <v>6971241</v>
+        <v>6971254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131194524</v>
       </c>
       <c r="B24" t="n">
-        <v>80390</v>
+        <v>80391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>80314</v>
+        <v>80315</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B27" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,34 +3426,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R27" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,42 +3546,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R28" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3605,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,12 +3615,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,7 +3645,7 @@
         <v>131194517</v>
       </c>
       <c r="B29" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>91818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R4" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1129,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,34 +1127,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R6" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194505</v>
+        <v>131194515</v>
       </c>
       <c r="B11" t="n">
-        <v>91818</v>
+        <v>92116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582448</v>
+        <v>582399</v>
       </c>
       <c r="R11" t="n">
-        <v>6971239</v>
+        <v>6971300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194515</v>
+        <v>131194505</v>
       </c>
       <c r="B12" t="n">
-        <v>92116</v>
+        <v>91818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582399</v>
+        <v>582448</v>
       </c>
       <c r="R12" t="n">
-        <v>6971300</v>
+        <v>6971239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B17" t="n">
-        <v>91818</v>
+        <v>80355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R17" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B18" t="n">
-        <v>80355</v>
+        <v>91818</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R18" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,7 +2533,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131194513</v>
+        <v>131194504</v>
       </c>
       <c r="B19" t="n">
         <v>57888</v>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582374</v>
+        <v>582453</v>
       </c>
       <c r="R19" t="n">
-        <v>6971257</v>
+        <v>6971221</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,7 +2653,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131194504</v>
+        <v>131194513</v>
       </c>
       <c r="B20" t="n">
         <v>57888</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582453</v>
+        <v>582374</v>
       </c>
       <c r="R20" t="n">
-        <v>6971221</v>
+        <v>6971257</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>80315</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R25" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B26" t="n">
-        <v>80315</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R26" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194520</v>
+        <v>131194525</v>
       </c>
       <c r="B4" t="n">
-        <v>91818</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582466</v>
+        <v>582468</v>
       </c>
       <c r="R4" t="n">
-        <v>6971369</v>
+        <v>6971420</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194525</v>
+        <v>131194497</v>
       </c>
       <c r="B5" t="n">
         <v>57888</v>
@@ -1029,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1039,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582468</v>
+        <v>582449</v>
       </c>
       <c r="R5" t="n">
-        <v>6971420</v>
+        <v>6971290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,12 +1097,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194497</v>
+        <v>131194520</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>91818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582449</v>
+        <v>582466</v>
       </c>
       <c r="R6" t="n">
-        <v>6971290</v>
+        <v>6971369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194522</v>
       </c>
       <c r="B2" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194502</v>
+        <v>131194520</v>
       </c>
       <c r="B3" t="n">
-        <v>92116</v>
+        <v>91821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582445</v>
+        <v>582466</v>
       </c>
       <c r="R3" t="n">
-        <v>6971210</v>
+        <v>6971369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>131194525</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194497</v>
+        <v>131194502</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>92119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,42 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582449</v>
+        <v>582445</v>
       </c>
       <c r="R5" t="n">
-        <v>6971290</v>
+        <v>6971210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,12 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194520</v>
+        <v>131194497</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,34 +1127,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582466</v>
+        <v>582449</v>
       </c>
       <c r="R6" t="n">
-        <v>6971369</v>
+        <v>6971290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1239,7 @@
         <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>131194523</v>
       </c>
       <c r="B9" t="n">
-        <v>80390</v>
+        <v>80393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>131194501</v>
       </c>
       <c r="B10" t="n">
-        <v>80259</v>
+        <v>80262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>131194515</v>
       </c>
       <c r="B11" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194505</v>
+        <v>131194506</v>
       </c>
       <c r="B12" t="n">
-        <v>91818</v>
+        <v>80387</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582448</v>
+        <v>582440</v>
       </c>
       <c r="R12" t="n">
-        <v>6971239</v>
+        <v>6971241</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194506</v>
+        <v>131194505</v>
       </c>
       <c r="B13" t="n">
-        <v>80384</v>
+        <v>91821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582440</v>
+        <v>582448</v>
       </c>
       <c r="R13" t="n">
-        <v>6971241</v>
+        <v>6971239</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,7 +1988,7 @@
         <v>131194499</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>131194508</v>
       </c>
       <c r="B15" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>131194498</v>
       </c>
       <c r="B16" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B17" t="n">
-        <v>80355</v>
+        <v>91821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R17" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B18" t="n">
-        <v>91818</v>
+        <v>80358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R18" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,7 +2536,7 @@
         <v>131194504</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>131194513</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194507</v>
+        <v>131194510</v>
       </c>
       <c r="B21" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582437</v>
+        <v>582423</v>
       </c>
       <c r="R21" t="n">
-        <v>6971241</v>
+        <v>6971254</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194510</v>
+        <v>131194507</v>
       </c>
       <c r="B22" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582423</v>
+        <v>582437</v>
       </c>
       <c r="R22" t="n">
-        <v>6971254</v>
+        <v>6971241</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131194524</v>
       </c>
       <c r="B24" t="n">
-        <v>80391</v>
+        <v>80394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194512</v>
+        <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>80315</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582416</v>
+        <v>582421</v>
       </c>
       <c r="R25" t="n">
-        <v>6971268</v>
+        <v>6971304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,32 +3308,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194516</v>
+        <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>80318</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582421</v>
+        <v>582416</v>
       </c>
       <c r="R26" t="n">
-        <v>6971304</v>
+        <v>6971268</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194500</v>
+        <v>131194521</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>80358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,42 +3426,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582475</v>
+        <v>582470</v>
       </c>
       <c r="R27" t="n">
-        <v>6971060</v>
+        <v>6971407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3485,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3495,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194521</v>
+        <v>131194500</v>
       </c>
       <c r="B28" t="n">
-        <v>80355</v>
+        <v>57891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,34 +3533,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582470</v>
+        <v>582475</v>
       </c>
       <c r="R28" t="n">
-        <v>6971407</v>
+        <v>6971060</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3615,7 +3610,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,7 +3645,7 @@
         <v>131194517</v>
       </c>
       <c r="B29" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194522</v>
       </c>
       <c r="B2" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131194520</v>
       </c>
       <c r="B3" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194525</v>
+        <v>131194502</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>92120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582468</v>
+        <v>582445</v>
       </c>
       <c r="R4" t="n">
-        <v>6971420</v>
+        <v>6971210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194502</v>
+        <v>131194525</v>
       </c>
       <c r="B5" t="n">
-        <v>92119</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582445</v>
+        <v>582468</v>
       </c>
       <c r="R5" t="n">
-        <v>6971210</v>
+        <v>6971420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1084,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,7 +1119,7 @@
         <v>131194497</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B7" t="n">
-        <v>91821</v>
+        <v>80359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R7" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B8" t="n">
-        <v>80358</v>
+        <v>91822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R8" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194523</v>
+        <v>131194501</v>
       </c>
       <c r="B9" t="n">
-        <v>80393</v>
+        <v>80263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582470</v>
+        <v>582435</v>
       </c>
       <c r="R9" t="n">
-        <v>6971407</v>
+        <v>6971209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194501</v>
+        <v>131194523</v>
       </c>
       <c r="B10" t="n">
-        <v>80262</v>
+        <v>80394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582435</v>
+        <v>582470</v>
       </c>
       <c r="R10" t="n">
-        <v>6971209</v>
+        <v>6971407</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,7 +1667,7 @@
         <v>131194515</v>
       </c>
       <c r="B11" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>131194506</v>
       </c>
       <c r="B12" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131194505</v>
       </c>
       <c r="B13" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>131194499</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>131194508</v>
       </c>
       <c r="B15" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>131194498</v>
       </c>
       <c r="B16" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194503</v>
+        <v>131194518</v>
       </c>
       <c r="B17" t="n">
-        <v>91821</v>
+        <v>80359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582447</v>
+        <v>582445</v>
       </c>
       <c r="R17" t="n">
-        <v>6971212</v>
+        <v>6971383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194518</v>
+        <v>131194503</v>
       </c>
       <c r="B18" t="n">
-        <v>80358</v>
+        <v>91822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R18" t="n">
-        <v>6971383</v>
+        <v>6971212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131194504</v>
+        <v>131194513</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582453</v>
+        <v>582374</v>
       </c>
       <c r="R19" t="n">
-        <v>6971221</v>
+        <v>6971257</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131194513</v>
+        <v>131194504</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582374</v>
+        <v>582453</v>
       </c>
       <c r="R20" t="n">
-        <v>6971257</v>
+        <v>6971221</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194510</v>
+        <v>131194507</v>
       </c>
       <c r="B21" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582423</v>
+        <v>582437</v>
       </c>
       <c r="R21" t="n">
-        <v>6971254</v>
+        <v>6971241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194507</v>
+        <v>131194510</v>
       </c>
       <c r="B22" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582437</v>
+        <v>582423</v>
       </c>
       <c r="R22" t="n">
-        <v>6971241</v>
+        <v>6971254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,7 +2990,7 @@
         <v>131194509</v>
       </c>
       <c r="B23" t="n">
-        <v>91784</v>
+        <v>91785</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131194524</v>
       </c>
       <c r="B24" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>131194516</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>131194512</v>
       </c>
       <c r="B26" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>131194521</v>
       </c>
       <c r="B27" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>131194500</v>
       </c>
       <c r="B28" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>131194517</v>
       </c>
       <c r="B29" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>131194526</v>
       </c>
       <c r="B30" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194511</v>
+        <v>131194514</v>
       </c>
       <c r="B7" t="n">
-        <v>80359</v>
+        <v>91822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582418</v>
+        <v>582404</v>
       </c>
       <c r="R7" t="n">
-        <v>6971267</v>
+        <v>6971295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194514</v>
+        <v>131194511</v>
       </c>
       <c r="B8" t="n">
-        <v>91822</v>
+        <v>80359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582404</v>
+        <v>582418</v>
       </c>
       <c r="R8" t="n">
-        <v>6971295</v>
+        <v>6971267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1771,32 +1771,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194506</v>
+        <v>131194505</v>
       </c>
       <c r="B12" t="n">
-        <v>80388</v>
+        <v>91822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582440</v>
+        <v>582448</v>
       </c>
       <c r="R12" t="n">
-        <v>6971241</v>
+        <v>6971239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194505</v>
+        <v>131194506</v>
       </c>
       <c r="B13" t="n">
-        <v>91822</v>
+        <v>80388</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582448</v>
+        <v>582440</v>
       </c>
       <c r="R13" t="n">
-        <v>6971239</v>
+        <v>6971241</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194522</v>
+        <v>131194502</v>
       </c>
       <c r="B2" t="n">
-        <v>80325</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582470</v>
+        <v>582445</v>
       </c>
       <c r="R2" t="n">
-        <v>6971407</v>
+        <v>6971210</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194520</v>
+        <v>131194515</v>
       </c>
       <c r="B3" t="n">
-        <v>91828</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582466</v>
+        <v>582399</v>
       </c>
       <c r="R3" t="n">
-        <v>6971369</v>
+        <v>6971300</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194502</v>
+        <v>131194503</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582445</v>
+        <v>582447</v>
       </c>
       <c r="R4" t="n">
-        <v>6971210</v>
+        <v>6971212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194525</v>
+        <v>131194505</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582468</v>
+        <v>582448</v>
       </c>
       <c r="R5" t="n">
-        <v>6971420</v>
+        <v>6971239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194497</v>
+        <v>131194514</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582449</v>
+        <v>582404</v>
       </c>
       <c r="R6" t="n">
-        <v>6971290</v>
+        <v>6971295</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194511</v>
+        <v>131194520</v>
       </c>
       <c r="B7" t="n">
-        <v>80365</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582418</v>
+        <v>582466</v>
       </c>
       <c r="R7" t="n">
-        <v>6971267</v>
+        <v>6971369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194514</v>
+        <v>131194509</v>
       </c>
       <c r="B8" t="n">
-        <v>91828</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582404</v>
+        <v>582422</v>
       </c>
       <c r="R8" t="n">
-        <v>6971295</v>
+        <v>6971247</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194501</v>
+        <v>131194516</v>
       </c>
       <c r="B9" t="n">
-        <v>80269</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582435</v>
+        <v>582421</v>
       </c>
       <c r="R9" t="n">
-        <v>6971209</v>
+        <v>6971304</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194523</v>
+        <v>131194501</v>
       </c>
       <c r="B10" t="n">
-        <v>80400</v>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582470</v>
+        <v>582435</v>
       </c>
       <c r="R10" t="n">
-        <v>6971407</v>
+        <v>6971209</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194505</v>
+        <v>131194498</v>
       </c>
       <c r="B11" t="n">
-        <v>91828</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582448</v>
+        <v>582466</v>
       </c>
       <c r="R11" t="n">
-        <v>6971239</v>
+        <v>6971193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194506</v>
+        <v>131194508</v>
       </c>
       <c r="B12" t="n">
-        <v>80394</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,7 +1780,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582440</v>
+        <v>582438</v>
       </c>
       <c r="R12" t="n">
         <v>6971241</v>
@@ -1841,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194515</v>
+        <v>131194511</v>
       </c>
       <c r="B13" t="n">
-        <v>92126</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582399</v>
+        <v>582418</v>
       </c>
       <c r="R13" t="n">
-        <v>6971300</v>
+        <v>6971267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194499</v>
+        <v>131194517</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,42 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582482</v>
+        <v>582448</v>
       </c>
       <c r="R14" t="n">
-        <v>6971060</v>
+        <v>6971341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194508</v>
+        <v>131194518</v>
       </c>
       <c r="B15" t="n">
-        <v>80365</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582438</v>
+        <v>582445</v>
       </c>
       <c r="R15" t="n">
-        <v>6971241</v>
+        <v>6971383</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194498</v>
+        <v>131194521</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582466</v>
+        <v>582470</v>
       </c>
       <c r="R16" t="n">
-        <v>6971193</v>
+        <v>6971407</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194503</v>
+        <v>131194526</v>
       </c>
       <c r="B17" t="n">
-        <v>91828</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582447</v>
+        <v>582489</v>
       </c>
       <c r="R17" t="n">
-        <v>6971212</v>
+        <v>6971407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194518</v>
+        <v>131194506</v>
       </c>
       <c r="B18" t="n">
-        <v>80365</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582445</v>
+        <v>582440</v>
       </c>
       <c r="R18" t="n">
-        <v>6971383</v>
+        <v>6971241</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,53 +2494,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131194513</v>
+        <v>131194523</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>80467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582374</v>
+        <v>582470</v>
       </c>
       <c r="R19" t="n">
-        <v>6971257</v>
+        <v>6971407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2621,12 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,53 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131194504</v>
+        <v>131194524</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>80468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582453</v>
+        <v>582468</v>
       </c>
       <c r="R20" t="n">
-        <v>6971221</v>
+        <v>6971409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2741,12 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,45 +2708,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194510</v>
+        <v>131194497</v>
       </c>
       <c r="B21" t="n">
-        <v>80325</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582423</v>
+        <v>582449</v>
       </c>
       <c r="R21" t="n">
-        <v>6971254</v>
+        <v>6971290</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2786,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2796,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,45 +2828,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194507</v>
+        <v>131194499</v>
       </c>
       <c r="B22" t="n">
-        <v>80325</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582437</v>
+        <v>582482</v>
       </c>
       <c r="R22" t="n">
-        <v>6971241</v>
+        <v>6971060</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2906,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2916,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,45 +2948,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131194509</v>
+        <v>131194500</v>
       </c>
       <c r="B23" t="n">
-        <v>91791</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582422</v>
+        <v>582475</v>
       </c>
       <c r="R23" t="n">
-        <v>6971247</v>
+        <v>6971060</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3057,7 +3026,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3067,7 +3036,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,45 +3068,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131194524</v>
+        <v>131194504</v>
       </c>
       <c r="B24" t="n">
-        <v>80401</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582468</v>
+        <v>582453</v>
       </c>
       <c r="R24" t="n">
-        <v>6971409</v>
+        <v>6971221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3164,7 +3146,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3174,7 +3156,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3201,45 +3188,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194512</v>
+        <v>131194513</v>
       </c>
       <c r="B25" t="n">
-        <v>80325</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582416</v>
+        <v>582374</v>
       </c>
       <c r="R25" t="n">
-        <v>6971268</v>
+        <v>6971257</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3276,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194516</v>
+        <v>131194525</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,34 +3319,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582421</v>
+        <v>582468</v>
       </c>
       <c r="R26" t="n">
-        <v>6971304</v>
+        <v>6971420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3386,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3396,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,27 +3428,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194500</v>
+        <v>131194519</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>5199</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3444,11 +3457,12 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3458,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582475</v>
+        <v>582458</v>
       </c>
       <c r="R27" t="n">
-        <v>6971060</v>
+        <v>6971363</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3517,6 +3526,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3535,32 +3545,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131194521</v>
+        <v>131194507</v>
       </c>
       <c r="B28" t="n">
-        <v>80365</v>
+        <v>80392</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3570,10 +3580,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582470</v>
+        <v>582437</v>
       </c>
       <c r="R28" t="n">
-        <v>6971407</v>
+        <v>6971241</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,7 +3615,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3615,7 +3625,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3642,32 +3652,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131194517</v>
+        <v>131194510</v>
       </c>
       <c r="B29" t="n">
-        <v>80365</v>
+        <v>80392</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3677,10 +3687,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582448</v>
+        <v>582423</v>
       </c>
       <c r="R29" t="n">
-        <v>6971341</v>
+        <v>6971254</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3712,7 +3722,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3722,7 +3732,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3749,32 +3759,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131194526</v>
+        <v>131194512</v>
       </c>
       <c r="B30" t="n">
-        <v>80365</v>
+        <v>80392</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3784,10 +3794,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582489</v>
+        <v>582416</v>
       </c>
       <c r="R30" t="n">
-        <v>6971407</v>
+        <v>6971268</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3819,7 +3829,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3829,7 +3839,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,10 +3866,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131194519</v>
+        <v>131194522</v>
       </c>
       <c r="B31" t="n">
-        <v>5197</v>
+        <v>80392</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,43 +3877,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skallberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582458</v>
+        <v>582470</v>
       </c>
       <c r="R31" t="n">
-        <v>6971363</v>
+        <v>6971407</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3936,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3945,7 +3946,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3954,7 +3955,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3379-2026 artfynd.xlsx
+++ b/artfynd/A 3379-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194502</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194515</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194503</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194505</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194514</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194520</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194509</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194516</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194501</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194498</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194508</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194511</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194517</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194518</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194521</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194526</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194523</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194524</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2825,6 +2925,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194497</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2945,6 +3050,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194499</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3065,6 +3175,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194500</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3185,6 +3300,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194504</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3305,6 +3425,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194513</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3425,6 +3550,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194525</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3542,6 +3672,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194519</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3649,6 +3784,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194507</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3756,6 +3896,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194510</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3863,6 +4008,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194512</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3970,8 +4120,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194522</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>